--- a/deliverables/24i3015_24i3166_24i3158_B.xlsx
+++ b/deliverables/24i3015_24i3166_24i3158_B.xlsx
@@ -1491,7 +1491,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>expected conf&lt;1 under a stricter spec; contradicts confirmed F-09 characterization (conf=1) -- awaiting human-approved oracle</t>
+          <t>expected conf&lt;1 under a stricter spec; contradicts confirmed F-09 characterization (conf=1) -- oracle approved as the correct reading 2026-10-01 (F-09 resolved as a confirmed defect)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>expected state!=0 under a stricter spec; contradicts confirmed F-10 characterization (state=0) -- awaiting human-approved oracle</t>
+          <t>expected state!=0 under a stricter spec; contradicts confirmed F-10 characterization (state=0) -- oracle approved as the correct reading 2026-10-01 (F-10 resolved as a confirmed defect)</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">

--- a/deliverables/24i3015_24i3166_24i3158_B.xlsx
+++ b/deliverables/24i3015_24i3166_24i3158_B.xlsx
@@ -1491,7 +1491,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>expected conf&lt;1 under a stricter spec; contradicts confirmed F-09 characterization (conf=1) -- oracle approved as the correct reading 2026-10-01 (F-09 resolved as a confirmed defect)</t>
+          <t>expected conf&lt;1 under a stricter spec; contradicts confirmed F-09 characterization (conf=1) -- stricter oracle proposed 2026-10-01 (F-09 candidate defect, pending whole-team review)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>expected state!=0 under a stricter spec; contradicts confirmed F-10 characterization (state=0) -- oracle approved as the correct reading 2026-10-01 (F-10 resolved as a confirmed defect)</t>
+          <t>expected state!=0 under a stricter spec; contradicts confirmed F-10 characterization (state=0) -- stricter oracle proposed 2026-10-01 (F-10 candidate defect, pending whole-team review)</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Construct/destroy groups of size 0..5 (one with an extra add_new_validator()) without crashing</t>
+          <t>Constructor links exactly n siblings for sizes 0..5; add_new_validator() appends a reachable sibling; destructor walks every sibling (smoke)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>no crash</t>
+          <t>get_sensor_state(i)!=UINT32_MAX for all i&lt;n and ==UINT32_MAX at i==n; after add_new_validator() on g(3): index 3 found, index 4 not found; destructor runs without crash (freeing not observable via API) [DataValidatorGroup.cpp L54-65, L74-80, L83-95, L313-328]</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>DVG-D04</t>
+          <t>DVG-D01 T/F; DVG-D02 T/F; DVG-D04; DVG-D35/D36 T/F</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>expected: ASan-detected out-of-bounds write on esc[8] (only observable under ASan, confirmed real defect per work/basis/INVENTORY)</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>under ASan: the probe aborts with stack-buffer-overflow, READ at FailureInjector.cpp:118 (status.esc[8], one past the esc[8] array) -&gt; F-07a defect present. In a normal/Coverage build the probe is an inert SUCCEED() and proves nothing</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector.cpp ; evidence/tests/probes/functional-SqeFailureInjector_PRB0506.xml</t>
+          <t>FailureInjector.cpp ; sanitizer run: evidence/tests/sanitizer/asan_PRB05.log (ASan stack-buffer-overflow at FailureInjector.cpp:118; reproduce with tools/sqe_asan_probes.sh) -- fails as expected, defect F-07a confirmed at runtime</t>
         </is>
       </c>
     </row>
@@ -5355,12 +5355,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>expected: UBSan-detected 'shift exponent too large' (only observable under UBSan, confirmed real defect per work/basis/INVENTORY)</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>under UBSan (-fsanitize=shift): 'shift exponent 4294967195 is too large for 32-bit type int' at FailureInjector.cpp:120 -&gt; F-07b defect present. In a normal/Coverage build the probe is an inert SUCCEED() and proves nothing</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector.cpp ; evidence/tests/probes/functional-SqeFailureInjector_PRB0506.xml</t>
+          <t>FailureInjector.cpp ; sanitizer run: evidence/tests/sanitizer/ubsan_PRB06.log (UBSan shift-exponent runtime error at FailureInjector.cpp:120; reproduce with tools/sqe_ubsan_probes.sh) -- fails as expected, defect F-07b confirmed at runtime</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>unique-cause</t>
+          <t>unique-cause (short-circuit)</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">

--- a/deliverables/24i3015_24i3166_24i3158_B.xlsx
+++ b/deliverables/24i3015_24i3166_24i3158_B.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MC-DC Evidence" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Inventory'!$A$1:$H$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Inventory'!$A$1:$H$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MC-DC Evidence'!$A$1:$S$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>get_best=nullptr,idx=-1; failover_index=-1; failover_state=NO_ERROR; get_sensor_state=UINT32_MAX; get_sensor_priority=0; no crash</t>
+          <t>get_best() -&gt; nullptr, idx -1; failover_index -1; failover_state NO_ERROR; get_sensor_state UINT32_MAX; get_sensor_priority 0; print() emits exactly "validator: best: -1, prev best: -1, failsafe: NO (0 events)" and no "sensor #" line [DataValidatorGroup.cpp L250-256]</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -2059,27 +2059,27 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-01</t>
+          <t>SQE-DVG-13</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D13 E&amp;F true; D15 K&amp;L true)</t>
+          <t>DataValidatorGroup::print (NO_DATA flag on a used sensor)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Equal confidence higher priority candidate switches and is not counted as a failover</t>
+          <t>print() shows " OFF" for a fed sensor whose error mask still holds NO_DATA (closes former gap G-04)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,5,50)-&gt;get_best=0; put(1,T0+1000,v,5,75); get_best</t>
+          <t>g(1); get_best(T0) before any put (sets NO_DATA); put(0,T0+1000,v,0,50); print() before any further confidence()</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>idx=1; failover_count()=0</t>
+          <t>output contains "sensor #0, prio: 50, state: OFF" and no " OK" [DataValidatorGroup.cpp L256-266; DataValidator.cpp L106-108; state() returns _error_mask]</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>DVG-D13(E,F true) DVG-D15(K,L true)</t>
+          <t>DVG-D24 T; DVG-D25 T (" OFF" ternary, L260 record 10)</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2101,27 +2101,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-02</t>
+          <t>SQE-DVG-AF-01</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D13 F false pair of MC01)</t>
+          <t>DataValidatorGroup::add_new_validator (allocation failure)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Equal confidence equal priority candidate does not switch</t>
+          <t>add_new_validator() when operator new returns nullptr (NuttX -fcheck-new semantics) returns nullptr and leaves the group intact</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,5,50)-&gt;get_best=0; put(1,T0+1000,v,5,50); get_best</t>
+          <t>g(1) with sensor 0 fed; test-only global operator new fails the next allocation; then allocation restored</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>idx=0; failover_count()=0</t>
+          <t>returns nullptr; index 1 not found; get_best() still selects 0; control: a second call (allocation OK) returns non-null and index 1 is found [DataValidatorGroup.cpp L83-95]</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -2131,39 +2131,39 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>DVG-D13(F false)</t>
+          <t>DVG-D05 T; G-01 L86 null check, L88 T, L89</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup.cpp ; evidence/tests/xml/unit-SqeDataValidatorGroup.xml</t>
+          <t>DataValidatorGroup.cpp ; evidence/tests/xml/unit-SqeDataValidatorGroupAlloc.xml</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-03</t>
+          <t>SQE-DVG-AF-02</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D13 E false pair of MC01)</t>
+          <t>DataValidatorGroup ctor (allocation failure)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Lower confidence higher priority candidate does not switch</t>
+          <t>Constructor survives its only allocation returning nullptr and yields an empty group</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,5,50)-&gt;get_best=0; put(1,T0+1000,v,7,75); get_best</t>
+          <t>operator new fails the 1st allocation; DataValidatorGroup(1)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>idx=0</t>
+          <t>no crash; get_sensor_state(0)==UINT32_MAX; get_best() -&gt; nullptr, idx -1 [DataValidatorGroup.cpp L48-72]</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2173,39 +2173,39 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>DVG-D13(E false)</t>
+          <t>G-01 L55 null result; DVG-D02 T; DVG-D03 F</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup.cpp ; evidence/tests/xml/unit-SqeDataValidatorGroup.xml</t>
+          <t>DataValidatorGroup.cpp ; evidence/tests/xml/unit-SqeDataValidatorGroupAlloc.xml</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-04</t>
+          <t>SQE-DVG-AF-03</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D13 C&amp;D true; D15 L false; F-11)</t>
+          <t>DataValidatorGroup ctor (allocation failure, F-13)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Higher confidence equal-priority candidate switches and IS counted as a failover (characterization F-11)</t>
+          <t>characterization (F-13): a failed middle allocation in the constructor dereferences a null prev</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,5,50)-&gt;get_best=0; put(1,T0+1000,v,3,50); get_best</t>
+          <t>operator new fails the 2nd allocation; DataValidatorGroup(3) inside EXPECT_DEATH</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>idx=1; failover_count()=1</t>
+          <t>process dies: prev becomes nullptr at i=1 and prev-&gt;setSibling() at i=2 dereferences it [DataValidatorGroup.cpp L54-65]</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2215,39 +2215,39 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>DVG-D13(C,D true) DVG-D15(L false)</t>
+          <t>DVG-D02 F; F-13 runtime evidence</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup.cpp ; evidence/tests/xml/unit-SqeDataValidatorGroup.xml</t>
+          <t>DataValidatorGroup.cpp ; evidence/tests/xml/unit-SqeDataValidatorGroupAlloc.xml</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-05</t>
+          <t>SQE-DVG-MC-01</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D13 D false pair of MC04)</t>
+          <t>DataValidatorGroup::get_best (D13 E&amp;F true; D15 K&amp;L true)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Higher confidence lower priority candidate does not switch</t>
+          <t>Equal confidence higher priority candidate switches and is not counted as a failover</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,5,50)-&gt;get_best=0; put(1,T0+1000,v,3,25); get_best</t>
+          <t>g(2); put(0,T0,v,5,50)-&gt;get_best=0; put(1,T0+1000,v,5,75); get_best</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>idx=0</t>
+          <t>idx=1; failover_count()=0</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>DVG-D13(D false)</t>
+          <t>DVG-D13(E,F true) DVG-D15(K,L true)</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2269,27 +2269,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-06</t>
+          <t>SQE-DVG-MC-02</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D13 C false pair of MC04)</t>
+          <t>DataValidatorGroup::get_best (D13 F false pair of MC01)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Lower confidence equal priority candidate does not switch</t>
+          <t>Equal confidence equal priority candidate does not switch</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,5,50)-&gt;get_best=0; put(1,T0+1000,v,7,50); get_best</t>
+          <t>g(2); put(0,T0,v,5,50)-&gt;get_best=0; put(1,T0+1000,v,5,50); get_best</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>idx=0</t>
+          <t>idx=0; failover_count()=0</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>DVG-D13(C false)</t>
+          <t>DVG-D13(F false)</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2311,27 +2311,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-07</t>
+          <t>SQE-DVG-MC-03</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D13 A true pair of MC08)</t>
+          <t>DataValidatorGroup::get_best (D13 E false pair of MC01)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Below-threshold confidence replaced by above-threshold confidence switches regardless of priority</t>
+          <t>Lower confidence higher priority candidate does not switch</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,11,50)-&gt;get_best=0; put(1,T0+1000,v,5,25); get_best</t>
+          <t>g(2); put(0,T0,v,5,50)-&gt;get_best=0; put(1,T0+1000,v,7,75); get_best</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>idx=1; failover_count()=1</t>
+          <t>idx=0</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>DVG-D13(A true)</t>
+          <t>DVG-D13(E false)</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2353,27 +2353,27 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-08</t>
+          <t>SQE-DVG-MC-04</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D13 A false pair of MC07)</t>
+          <t>DataValidatorGroup::get_best (D13 C&amp;D true; D15 L false; F-11)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Above-threshold confidence vs lower-priority above-threshold candidate: no switch</t>
+          <t>Higher confidence equal-priority candidate switches and IS counted as a failover (characterization F-11)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,9,50)-&gt;get_best=0; put(1,T0+1000,v,5,25); get_best</t>
+          <t>g(2); put(0,T0,v,5,50)-&gt;get_best=0; put(1,T0+1000,v,3,50); get_best</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>idx=0</t>
+          <t>idx=1; failover_count()=1</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>DVG-D13(A false)</t>
+          <t>DVG-D13(C,D true) DVG-D15(L false)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2395,27 +2395,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-09</t>
+          <t>SQE-DVG-MC-05</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D13 B true pair of MC10)</t>
+          <t>DataValidatorGroup::get_best (D13 D false pair of MC04)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Far-below-threshold confidence replaced by above-threshold confidence switches</t>
+          <t>Higher confidence lower priority candidate does not switch</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,20,50)-&gt;get_best=0; put(1,T0+1000,v,5,25); get_best</t>
+          <t>g(2); put(0,T0,v,5,50)-&gt;get_best=0; put(1,T0+1000,v,3,25); get_best</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>idx=1; failover_count()=1</t>
+          <t>idx=0</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>DVG-D13(B true)</t>
+          <t>DVG-D13(D false)</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2437,22 +2437,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-10</t>
+          <t>SQE-DVG-MC-06</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D13 B false pair of MC09)</t>
+          <t>DataValidatorGroup::get_best (D13 C false pair of MC04)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Both below threshold lower priority candidate does not switch</t>
+          <t>Lower confidence equal priority candidate does not switch</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,20,50)-&gt;get_best=0; put(1,T0+1000,v,15,25); get_best</t>
+          <t>g(2); put(0,T0,v,5,50)-&gt;get_best=0; put(1,T0+1000,v,7,50); get_best</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>DVG-D13(B false)</t>
+          <t>DVG-D13(C false)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2479,27 +2479,27 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-11</t>
+          <t>SQE-DVG-MC-07</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D13 G false pair of MC12)</t>
+          <t>DataValidatorGroup::get_best (D13 A true pair of MC08)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>First-ever call with the only sensor never put: no candidate selected</t>
+          <t>Below-threshold confidence replaced by above-threshold confidence switches regardless of priority</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>g(2); get_best(T0) as first call ever (sensor0 never put)</t>
+          <t>g(2); put(0,T0,v,11,50)-&gt;get_best=0; put(1,T0+1000,v,5,25); get_best</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>idx=-1; pointer nullptr; failover_count()=0</t>
+          <t>idx=1; failover_count()=1</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>DVG-D13(G false)</t>
+          <t>DVG-D13(A true)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2521,22 +2521,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-12</t>
+          <t>SQE-DVG-MC-08</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D13 G true pair of MC11)</t>
+          <t>DataValidatorGroup::get_best (D13 A false pair of MC07)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>First-ever call with one sensor put selects it</t>
+          <t>Above-threshold confidence vs lower-priority above-threshold candidate: no switch</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,50,50); get_best(T0) as first call ever</t>
+          <t>g(2); put(0,T0,v,9,50)-&gt;get_best=0; put(1,T0+1000,v,5,25); get_best</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>DVG-D13(G true)</t>
+          <t>DVG-D13(A false)</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2563,27 +2563,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-13</t>
+          <t>SQE-DVG-MC-09</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best/failover_index/state (D14 H true; D32/D34 P&amp;Q&amp;R true)</t>
+          <t>DataValidatorGroup::get_best (D13 B true pair of MC10)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Real failover: sensor0 times out sensor1 takes over; failover_index/state report sensor0/TIMEOUT</t>
+          <t>Far-below-threshold confidence replaced by above-threshold confidence switches</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>g(2); 3-call sequence ending with sensor0 silent &gt;40ms; failover_index/state()</t>
+          <t>g(2); put(0,T0,v,20,50)-&gt;get_best=0; put(1,T0+1000,v,5,25); get_best</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>idx=1 at call3; failover_index()=0; failover_state()=TIMEOUT</t>
+          <t>idx=1; failover_count()=1</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>DVG-D14(H true) DVG-D32/D34(P,Q,R true)</t>
+          <t>DVG-D13(B true)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2605,27 +2605,27 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-14</t>
+          <t>SQE-DVG-MC-10</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D14 H false pair of MC13)</t>
+          <t>DataValidatorGroup::get_best (D13 B false pair of MC09)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Stable sensor keeps winning on priority: no failover</t>
+          <t>Both below threshold lower priority candidate does not switch</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,0,50)-&gt;get_best=0; put(1,T0+1,v,0,40); get_best</t>
+          <t>g(2); put(0,T0,v,20,50)-&gt;get_best=0; put(1,T0+1000,v,15,25); get_best</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>idx=0; failover_count()=0</t>
+          <t>idx=0</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>DVG-D14(H false)</t>
+          <t>DVG-D13(B false)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2647,27 +2647,27 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-18</t>
+          <t>SQE-DVG-MC-11</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D14 H false I false control row)</t>
+          <t>DataValidatorGroup::get_best (D13 G false pair of MC12)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Single-sensor stable fresh data: no failover</t>
+          <t>First-ever call with the only sensor never put: no candidate selected</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>g(1); put(0,T0,v,0,50)-&gt;get_best=0; put(0,T0+1000,v,0,50); get_best</t>
+          <t>g(2); get_best(T0) as first call ever (sensor0 never put)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>idx=0; failover_count()=0</t>
+          <t>idx=-1; pointer nullptr; failover_count()=0</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>DVG-D14(H false I false)</t>
+          <t>DVG-D13(G false)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2689,27 +2689,27 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-19</t>
+          <t>SQE-DVG-MC-12</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D14 I&amp;J true pair of MC18/MC20)</t>
+          <t>DataValidatorGroup::get_best (D13 G true pair of MC11)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Single sensor silent past timeout triggers failover via confidence drop (not H); F-02 non-null pointer</t>
+          <t>First-ever call with one sensor put selects it</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>continuing MC18 setup; get_best() &gt;40000us after last put</t>
+          <t>g(2); put(0,T0,v,50,50); get_best(T0) as first call ever</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>idx=-1; failover_count()=1; pointer != nullptr</t>
+          <t>idx=0</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>DVG-D14(I,J true) DVG-D20T</t>
+          <t>DVG-D13(G true)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2731,27 +2731,27 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-20</t>
+          <t>SQE-DVG-MC-13</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D14 J false control row pair of MC19)</t>
+          <t>DataValidatorGroup::get_best/failover_index/state (D14 H true; D32/D34 P&amp;Q&amp;R true)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Single sensor never fed: no candidate selected on the first-ever call</t>
+          <t>Real failover: sensor0 times out sensor1 takes over; failover_index/state report sensor0/TIMEOUT</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>g(1); get_best(T0) as first call ever (never put)</t>
+          <t>g(2); 3-call sequence ending with sensor0 silent &gt;40ms; failover_index/state()</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>idx=-1; pointer nullptr; failover_count()=0</t>
+          <t>idx=1 at call3; failover_index()=0; failover_state()=TIMEOUT</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>DVG-D14(J false)</t>
+          <t>DVG-D14(H true) DVG-D32/D34(P,Q,R true)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2773,22 +2773,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-21</t>
+          <t>SQE-DVG-MC-14</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D15 K false control vector -- O3)</t>
+          <t>DataValidatorGroup::get_best (D14 H false pair of MC13)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>First-ever call with one sensor put: D15 evaluated with K false but has no observable effect (O3 row)</t>
+          <t>Stable sensor keeps winning on priority: no failover</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,50,50); get_best(T0) as first call ever</t>
+          <t>g(2); put(0,T0,v,0,50)-&gt;get_best=0; put(1,T0+1,v,0,40); get_best</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>DVG-D15(K false)</t>
+          <t>DVG-D14(H false)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2815,27 +2815,27 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-22</t>
+          <t>SQE-DVG-MC-18</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (D15 M false pair of MC01)</t>
+          <t>DataValidatorGroup::get_best (D14 H false I false control row)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Higher priority but large confidence jump still counts as a failover</t>
+          <t>Single-sensor stable fresh data: no failover</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>g(2); put(0,T0,v,50,50)-&gt;get_best=0; put(1,T0+1000,v,5,75); get_best</t>
+          <t>g(1); put(0,T0,v,0,50)-&gt;get_best=0; put(0,T0+1000,v,0,50); get_best</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>idx=1; failover_count()=1</t>
+          <t>idx=0; failover_count()=0</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>DVG-D15(M false)</t>
+          <t>DVG-D14(H false I false)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2857,27 +2857,27 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-23</t>
+          <t>SQE-DVG-MC-19</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::failover_index/state (D32/D34 Q false pair of MC13)</t>
+          <t>DataValidatorGroup::get_best (D14 I&amp;J true pair of MC18/MC20)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Sensor recovers after failover: failover_index/state report nothing (no longer erroring)</t>
+          <t>Single sensor silent past timeout triggers failover via confidence drop (not H); F-02 non-null pointer</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>continuing MC13 state; sensor0 fresh put then get_best; failover_index/state()</t>
+          <t>continuing MC18 setup; get_best() &gt;40000us after last put</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>failover_index()=-1; failover_state()=NO_ERROR</t>
+          <t>idx=-1; failover_count()=1; pointer != nullptr</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>DVG-D32/D34(Q false)</t>
+          <t>DVG-D14(I,J true) DVG-D20T</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2899,27 +2899,27 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-24</t>
+          <t>SQE-DVG-MC-20</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::failover_index/state (D32/D34 R false pair of MC13)</t>
+          <t>DataValidatorGroup::get_best (D14 J false control row pair of MC19)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Sensor that timed out but was never best is not reported by failover_index/state</t>
+          <t>Single sensor never fed: no candidate selected on the first-ever call</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>g(2); priority-tie bootstrap call then sensor1 times out while sensor0 stays best; failover_index/state()</t>
+          <t>g(1); get_best(T0) as first call ever (never put)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>failover_index()=-1; failover_state()=NO_ERROR</t>
+          <t>idx=-1; pointer nullptr; failover_count()=0</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>DVG-D32/D34(R false)</t>
+          <t>DVG-D14(J false)</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2941,27 +2941,27 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SQE-DVG-MC-25</t>
+          <t>SQE-DVG-MC-21</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::failover_index/state (D32/D34 P false pair of MC13; code-feasible/domain-invalid)</t>
+          <t>DataValidatorGroup::get_best (D15 K false control vector -- O3)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>put() with timestamp 0 resets used() so failover_index/state no longer report that sensor</t>
+          <t>First-ever call with one sensor put: D15 evaluated with K false but has no observable effect (O3 row)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>continuing MC13 state; put(0,0,v,0,50) (timestamp=0); failover_index/state()</t>
+          <t>g(2); put(0,T0,v,50,50); get_best(T0) as first call ever</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>failover_index()=-1; failover_state()=NO_ERROR</t>
+          <t>idx=0; failover_count()=0</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>DVG-D32/D34(P false)</t>
+          <t>DVG-D15(K false)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2983,69 +2983,69 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SQE-PRB-03</t>
+          <t>SQE-DVG-MC-22</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup::get_best (total-failure return-pointer probe)</t>
+          <t>DataValidatorGroup::get_best (D15 M false pair of MC01)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>probe (F-02): once nothing is selected (idx=-1) get_best() should arguably return nullptr</t>
+          <t>Higher priority but large confidence jump still counts as a failover</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>g(2); sensor0 best then both time out; get_best()</t>
+          <t>g(2); put(0,T0,v,50,50)-&gt;get_best=0; put(1,T0+1000,v,5,75); get_best</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>expected nullptr under a stricter reading of the header 'pointer to the array of best values'; contradicts confirmed F-02 characterization (DVG11, non-null) -- awaiting human-approved oracle</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>idx=1; failover_count()=1</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>DVG-D21 (same as DVG11)</t>
+          <t>DVG-D15(M false)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>DataValidatorGroup.cpp ; evidence/tests/probes/unit-SqeDataValidatorGroup.xml</t>
+          <t>DataValidatorGroup.cpp ; evidence/tests/xml/unit-SqeDataValidatorGroup.xml</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-01</t>
+          <t>SQE-DVG-MC-23</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::update/updateAttitudeStatus</t>
+          <t>DataValidatorGroup::failover_index/state (D32/D34 Q false pair of MC13)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Attitude control disabled resets all attitude flags and reports a status change</t>
+          <t>Sensor recovers after failover: failover_index/state report nothing (no longer erroring)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>roll 70 deg settled past hysteresis; then flag_control_attitude_enabled=false</t>
+          <t>continuing MC13 state; sensor0 fresh put then get_best; failover_index/state()</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>roll/pitch/alt/ext all false; update() returns true [FailureDetector.cpp L56-68]</t>
+          <t>failover_index()=-1; failover_state()=NO_ERROR</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -3055,39 +3055,39 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>FD-D01 (T then F)</t>
+          <t>DVG-D32/D34(Q false)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
+          <t>DataValidatorGroup.cpp ; evidence/tests/xml/unit-SqeDataValidatorGroup.xml</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-02</t>
+          <t>SQE-DVG-MC-24</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateAttitudeStatus</t>
+          <t>DataValidatorGroup::failover_index/state (D32/D34 R false pair of MC13)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Roll beyond limit sets flag after hysteresis settles</t>
+          <t>Sensor that timed out but was never best is not reported by failover_index/state</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>FD_FAIL_R_TTRI 0.02s; roll 70 deg; update(); wait 40ms; publish+update()</t>
+          <t>g(2); priority-tie bootstrap call then sensor1 times out while sensor0 stays best; failover_index/state()</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>first update roll=false; second roll=true; update() returns true [L118-136]</t>
+          <t>failover_index()=-1; failover_state()=NO_ERROR</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -3097,39 +3097,39 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>FD-D08T FD-D12(T,T)</t>
+          <t>DVG-D32/D34(R false)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
+          <t>DataValidatorGroup.cpp ; evidence/tests/xml/unit-SqeDataValidatorGroup.xml</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-03</t>
+          <t>SQE-DVG-MC-25</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateAttitudeStatus</t>
+          <t>DataValidatorGroup::failover_index/state (D32/D34 P false pair of MC13; code-feasible/domain-invalid)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Roll within limit never sets flag</t>
+          <t>put() with timestamp 0 resets used() so failover_index/state no longer report that sensor</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>FD_FAIL_R_TTRI 0.02s; roll 50 deg settled</t>
+          <t>continuing MC13 state; put(0,0,v,0,50) (timestamp=0); failover_index/state()</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>roll flag stays false [L123]</t>
+          <t>failover_index()=-1; failover_state()=NO_ERROR</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -3139,81 +3139,81 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>FD-D12(T,F)</t>
+          <t>DVG-D32/D34(P false)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
+          <t>DataValidatorGroup.cpp ; evidence/tests/xml/unit-SqeDataValidatorGroup.xml</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-04</t>
+          <t>SQE-PRB-03</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateAttitudeStatus</t>
+          <t>DataValidatorGroup::get_best (total-failure return-pointer probe)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Roll limit param 0 disables the check regardless of angle</t>
+          <t>probe (F-02): once nothing is selected (idx=-1) get_best() should arguably return nullptr</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>FD_FAIL_R 0; roll 170 deg settled</t>
+          <t>g(2); sensor0 best then both time out; get_best()</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>roll flag stays false (max_roll&gt;FLT_EPSILON False) [L123]</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>expected nullptr under a stricter reading of the header 'pointer to the array of best values'; contradicts confirmed F-02 characterization (DVG11, non-null) -- awaiting human-approved oracle</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>FD-D12 1st operand F</t>
+          <t>DVG-D21 (same as DVG11)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
+          <t>DataValidatorGroup.cpp ; evidence/tests/probes/unit-SqeDataValidatorGroup.xml</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-05</t>
+          <t>SQE-FD-01</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateAttitudeStatus</t>
+          <t>FailureDetector::update/updateAttitudeStatus</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Pitch beyond limit sets flag after hysteresis settles (pitch analogue of FD02)</t>
+          <t>Attitude control disabled resets all attitude flags and reports a status change</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>FD_FAIL_P_TTRI 0.02s; pitch 70 deg settled</t>
+          <t>roll 70 deg settled past hysteresis; then flag_control_attitude_enabled=false</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>pitch flag true [L124]</t>
+          <t>roll/pitch/alt/ext all false; update() returns true [FailureDetector.cpp L56-68]</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>FD-D13</t>
+          <t>FD-D01 (T then F)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3235,7 +3235,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-06</t>
+          <t>SQE-FD-02</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3245,17 +3245,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Pitch within limit never sets flag (pitch analogue of FD03)</t>
+          <t>Roll beyond limit sets flag after hysteresis settles</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>FD_FAIL_P_TTRI 0.02s; pitch 50 deg settled</t>
+          <t>FD_FAIL_R_TTRI 0.02s; roll 70 deg; update(); wait 40ms; publish+update()</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>pitch flag stays false [L124]</t>
+          <t>first update roll=false; second roll=true; update() returns true [L118-136]</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>FD-D13</t>
+          <t>FD-D08T FD-D12(T,T)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3277,7 +3277,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-07</t>
+          <t>SQE-FD-03</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3287,17 +3287,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Pitch limit param 0 disables the check (pitch analogue of FD04)</t>
+          <t>Roll within limit never sets flag</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>FD_FAIL_P 0; pitch 170 deg settled</t>
+          <t>FD_FAIL_R_TTRI 0.02s; roll 50 deg settled</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>pitch flag stays false [L124]</t>
+          <t>roll flag false at 50°; then, same detector, 70° -&gt; true (FALSE is value-driven, not a dead setup) [L123]</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>FD-D13</t>
+          <t>FD-D12 (T∧F) + positive control (T∧T)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3319,27 +3319,27 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-08</t>
+          <t>SQE-FD-04</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::update</t>
+          <t>FailureDetector::updateAttitudeStatus</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>No new attitude publish leaves flags unchanged and update() returns false</t>
+          <t>Roll limit param 0 disables the check regardless of angle</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>roll 70 deg settled true; second update() without new attitude publish</t>
+          <t>FD_FAIL_R 0; roll 170 deg settled</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>flags unchanged, roll stays true; update() returns false [L96]</t>
+          <t>roll flag false with FD_FAIL_R 0; control detector built with FD_FAIL_R 60 and the same 170° stimulus -&gt; true [L123]</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>FD-D08F</t>
+          <t>FD-D12 1st operand F</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-09</t>
+          <t>SQE-FD-05</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Tailsitter in transition disables the attitude check entirely</t>
+          <t>Pitch beyond limit sets flag after hysteresis settles (pitch analogue of FD02)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>is_vtol_tailsitter=true, in_transition_mode=true; roll 80 deg settled</t>
+          <t>FD_FAIL_P_TTRI 0.02s; pitch 70 deg settled</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>roll flag stays false (roll forced 0 during transition) [L103-107]</t>
+          <t>pitch flag true [L124]</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>FD-D09T FD-D10T</t>
+          <t>FD-D13</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-10</t>
+          <t>SQE-FD-06</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3413,17 +3413,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Tailsitter fixed-wing rotates attitude +90deg pitch before the check</t>
+          <t>Pitch within limit never sets flag (pitch analogue of FD03)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>tailsitter, not in transition, FIXED_WING; pitch -80 deg settled</t>
+          <t>FD_FAIL_P_TTRI 0.02s; pitch 50 deg settled</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>pitch flag false after rotation [L109-115]</t>
+          <t>pitch flag false at 50°; then, same detector, 70° -&gt; true [L124]</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>FD-D11T</t>
+          <t>FD-D13 (T∧F) + positive control</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3445,27 +3445,27 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-11</t>
+          <t>SQE-FD-07</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateExternalAtsStatus</t>
+          <t>FailureDetector::updateAttitudeStatus</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>External ATS pulse inside window sets ext flag after hysteresis</t>
+          <t>Pitch limit param 0 disables the check (pitch analogue of FD04)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>FD_EXT_ATS_EN 1; pulse 2000us; update(); wait 150ms; publish+update()</t>
+          <t>FD_FAIL_P 0; pitch 170 deg settled</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>ext flag true [L147-155]</t>
+          <t>pitch flag false with FD_FAIL_P 0 at 80°; control detector with FD_FAIL_P 60, same 80° stimulus -&gt; true. (80° not 170°: Euler pitch spans ±90°, 170° decomposes to pitch 10°/roll 180° and never trips the pitch check — the original 170° stimulus was vacuous, exposed by this control) [L124]</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>FD-D02T FD-D14T FD-D15(T,T)</t>
+          <t>FD-D13</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3487,27 +3487,27 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-12</t>
+          <t>SQE-FD-08</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateExternalAtsStatus</t>
+          <t>FailureDetector::update</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Pulse-width window boundaries are half-open [trig,3000)</t>
+          <t>No new attitude publish leaves flags unchanged and update() returns false</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>pulse 1899/1900/2999/3000, each its own detector, settled</t>
+          <t>roll 70 deg settled true; second update() without new attitude publish</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>false/true/true/false [L147]</t>
+          <t>flags unchanged, roll stays true; update() returns false [L96]</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>FD-D15 boundaries</t>
+          <t>FD-D08F</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3529,27 +3529,27 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-13</t>
+          <t>SQE-FD-09</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::update</t>
+          <t>FailureDetector::updateAttitudeStatus</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>External ATS disabled param keeps ext flag false regardless of pulse</t>
+          <t>Tailsitter in transition disables the attitude check entirely</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>FD_EXT_ATS_EN 0; pulse 2000us settled</t>
+          <t>is_vtol_tailsitter=true, in_transition_mode=true; roll 80 deg settled</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>ext flag stays false (updateExternalAtsStatus never called) [L59]</t>
+          <t>roll flag false during tailsitter transition; then transition ends (same detector) and the same 80° roll -&gt; true [L103-107]</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>FD-D02F</t>
+          <t>FD-D09T FD-D10T</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3571,27 +3571,27 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-14</t>
+          <t>SQE-FD-10</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateExternalAtsStatus</t>
+          <t>FailureDetector::updateAttitudeStatus</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>No new pwm_input leaves ext flag unchanged</t>
+          <t>Tailsitter fixed-wing rotates attitude +90deg pitch before the check</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>ATS enabled and settled true; second update() without new pwm_input publish</t>
+          <t>tailsitter, not in transition, FIXED_WING; pitch -80 deg settled</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>ext flag stays true [L144]</t>
+          <t>pitch flag false after rotation [L109-115]</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>FD-D14F</t>
+          <t>FD-D11T</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3613,27 +3613,27 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-15</t>
+          <t>SQE-FD-11</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateEscsStatus</t>
+          <t>FailureDetector::updateExternalAtsStatus</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>All ESCs armed with no failures keeps arm_escs false</t>
+          <t>External ATS pulse inside window sets ext flag after hysteresis</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>armed; 4 ESCs, armed_flags 0x0F, no per-ESC failures; settled</t>
+          <t>FD_EXT_ATS_EN 1; pulse 2000us; update(); wait 150ms; publish+update()</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>arm_escs false [L163-179]</t>
+          <t>ext flag true [L147-155]</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>FD-D03T FD-D04T FD-D16T FD-D17 FD-D18F FD-D19F</t>
+          <t>FD-D02T FD-D14T FD-D15(T,T)</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3655,27 +3655,27 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-16</t>
+          <t>SQE-FD-12</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateEscsStatus</t>
+          <t>FailureDetector::updateExternalAtsStatus</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Armed-mask mismatch sets arm_escs after 300ms hysteresis</t>
+          <t>Pulse-width window boundaries are half-open [trig,3000)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>armed; 4 ESCs, armed_flags 0x07 (expects 0x0F); settled</t>
+          <t>pulse 1899/1900/2999/3000, each its own detector, settled</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>arm_escs true, update() returns true [L174-179]</t>
+          <t>false/true/true/false [L147]</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>FD-D19T</t>
+          <t>FD-D15 boundaries</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3697,27 +3697,27 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-17</t>
+          <t>SQE-FD-13</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateEscsStatus</t>
+          <t>FailureDetector::update</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Per-ESC failures flag sets arm_escs even with a matching armed mask</t>
+          <t>External ATS disabled param keeps ext flag false regardless of pulse</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>armed; 4 ESCs armed_flags 0x0F (matches) but esc[0].failures=1; settled</t>
+          <t>FD_EXT_ATS_EN 0; pulse 2000us settled</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>arm_escs true [L171]</t>
+          <t>ext flag false with FD_EXT_ATS_EN 0; control detector with FD_EXT_ATS_EN 1, same 2000us pulse -&gt; true [L59]</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>FD-D18 2nd operand T</t>
+          <t>FD-D02F</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3739,27 +3739,27 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-18</t>
+          <t>SQE-FD-14</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateEscsStatus</t>
+          <t>FailureDetector::updateExternalAtsStatus</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>arm_escs stays latched true while armed even after ESCs become healthy</t>
+          <t>No new pwm_input leaves ext flag unchanged</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>trigger arm_escs true (FD16-style); then healthy ESC report settled while still armed</t>
+          <t>ATS enabled and settled true; second update() without new pwm_input publish</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>arm_escs stays true (no armed-branch reset to false) [L177-179]</t>
+          <t>ext flag stays true [L144]</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>FD-D19 no-else latch</t>
+          <t>FD-D14F</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-19</t>
+          <t>SQE-FD-15</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Disarmed state resets arm_escs synchronously</t>
+          <t>All ESCs armed with no failures keeps arm_escs false</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>disarmed; ESC mismatch that would trigger if armed; update()</t>
+          <t>armed; 4 ESCs, armed_flags 0x0F, no per-ESC failures; settled</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>arm_escs false immediately [L181-185]</t>
+          <t>arm_escs false with all 4 ESCs armed (0x0F); then, same detector, 0x07 for &gt;300ms -&gt; true [L163-179]</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>FD-D16F</t>
+          <t>FD-D03T FD-D04T FD-D16T FD-D17 FD-D18F FD-D19F</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-20</t>
+          <t>SQE-FD-16</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>esc_count above CONNECTED_ESC_MAX is clamped to 8 before the loop</t>
+          <t>Armed-mask mismatch sets arm_escs after 300ms hysteresis</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>armed; esc_count 12, armed_flags 0xFF (matches clamped 8-ESC mask); settled</t>
+          <t>armed; 4 ESCs, armed_flags 0x07 (expects 0x0F); settled</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>arm_escs false (clamp confirmed) [L164]</t>
+          <t>arm_escs true, update() returns true [L174-179]</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>FD-D17 clamp</t>
+          <t>FD-D19T</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3865,27 +3865,27 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-21</t>
+          <t>SQE-FD-17</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::update</t>
+          <t>FailureDetector::updateEscsStatus</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>ESCs check disabled param keeps arm_escs false regardless of report</t>
+          <t>Per-ESC failures flag sets arm_escs even with a matching armed mask</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>FD_ESCS_EN 0; armed_flags 0x00 (would trigger if enabled); settled</t>
+          <t>armed; 4 ESCs armed_flags 0x0F (matches) but esc[0].failures=1; settled</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>arm_escs stays false (updateEscsStatus never called) [L76]</t>
+          <t>arm_escs true [L171]</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>FD-D04F</t>
+          <t>FD-D18 2nd operand T</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3907,27 +3907,27 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-22</t>
+          <t>SQE-FD-18</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::update</t>
+          <t>FailureDetector::updateEscsStatus</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>No new esc_status publish skips both ESC and motor subroutines</t>
+          <t>arm_escs stays latched true while armed even after ESCs become healthy</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>esc_status published once, consumed; second update() without new publish</t>
+          <t>trigger arm_escs true (FD16-style); then healthy ESC report settled while still armed</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>getMotorFailures()=0, arm_escs unchanged, update() returns false [L73]</t>
+          <t>arm_escs stays true (no armed-branch reset to false) [L177-179]</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>FD-D03F</t>
+          <t>FD-D19 no-else latch</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3949,27 +3949,27 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-23</t>
+          <t>SQE-FD-19</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateMotorStatus</t>
+          <t>FailureDetector::updateEscsStatus</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>ESC telemetry timeout sets then clears the motor flag across 3 steps</t>
+          <t>Disarmed state resets arm_escs synchronously</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>ESC0 warmed with current; then stale timestamp (sets); repeat stale (stays); fresh timestamp (clears)</t>
+          <t>disarmed; ESC mismatch that would trigger if armed; update()</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>motor true then true then false; getMotorFailures()&amp;1 tracks it [L279-295]</t>
+          <t>arm_escs false while disarmed; then armed with the same 0x07 mismatch for &gt;300ms -&gt; true [L181-185]</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>FD-D32 FD-D33(T/F) FD-D34T FD-D42 FD-D43T FD-D44T</t>
+          <t>FD-D16F</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3991,27 +3991,27 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-24</t>
+          <t>SQE-FD-20</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateMotorStatus</t>
+          <t>FailureDetector::updateEscsStatus</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>ESC that never reports current never becomes 'valid', so timeout never flags</t>
+          <t>esc_count above CONNECTED_ESC_MAX is clamped to 8 before the loop</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>ESC0 esc_current always 0, old timestamp from the start</t>
+          <t>armed; esc_count 12, armed_flags 0xFF (matches clamped 8-ESC mask); settled</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>no timeout flag, getMotorFailures()=0 [L279,288,298]</t>
+          <t>arm_escs false for esc_count 12 with 0xFF (clamped to 8); control detector, same esc_count 12 with 0x7F -&gt; true (clamped mask still checks all 8 slots) [L164]</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>FD-D32F FD-D33F FD-D35F FD-D36F</t>
+          <t>FD-D17 clamp</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4033,27 +4033,27 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-25</t>
+          <t>SQE-FD-21</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateMotorStatus</t>
+          <t>FailureDetector::update</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Under-current while armed latches the motor flag after the configured timeout</t>
+          <t>ESCs check disabled param keeps arm_escs false regardless of report</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>FD_ACT_MOT_THR 0.2, C2T 2.0, TOUT 10ms; ESC0 warmed, then low current w/ high throttle; wait 30ms</t>
+          <t>FD_ESCS_EN 0; armed_flags 0x00 (would trigger if enabled); settled</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>motor flag true, update() returns true [L313-328]</t>
+          <t>arm_escs false with FD_ESCS_EN 0; control detector with FD_ESCS_EN 1, same 0x00 stimulus -&gt; true [L76]</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>FD-D36T FD-D37T FD-D38T FD-D39T FD-D41T</t>
+          <t>FD-D04F</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4075,27 +4075,27 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-26</t>
+          <t>SQE-FD-22</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateMotorStatus</t>
+          <t>FailureDetector::update</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Throttle dropping below threshold before the timeout resets the under-current timer</t>
+          <t>No new esc_status publish skips both ESC and motor subroutines</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>same params as FD25; throttle drops below threshold before 10ms elapses, then raised again</t>
+          <t>esc_status published once, consumed; second update() without new publish</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>motor flag stays false (timer restarted) [L318-322]</t>
+          <t>getMotorFailures()=0, arm_escs unchanged, update() returns false [L73]</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>FD-D38F FD-D40T</t>
+          <t>FD-D03F</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4117,7 +4117,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-27</t>
+          <t>SQE-FD-23</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4127,17 +4127,17 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>NaN actuator control is treated as zero throttle (guard, not crash)</t>
+          <t>ESC telemetry timeout sets then clears the motor flag across 3 steps</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>same params as FD25; actuator_motors.control[0]=NaN with low current</t>
+          <t>ESC0 warmed with current; then stale timestamp (sets); repeat stale (stays); fresh timestamp (clears)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>no under-current timer starts, motor stays false [L305-307]</t>
+          <t>motor true then true then false; getMotorFailures()&amp;1 tracks it [L279-295]</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>FD-D37F</t>
+          <t>FD-D32 FD-D33(T/F) FD-D34T FD-D42 FD-D43T FD-D44T</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-28</t>
+          <t>SQE-FD-24</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4169,17 +4169,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Non-motor actuator_function is skipped by the unsigned-wrap guard</t>
+          <t>ESC that never reports current never becomes 'valid', so timeout never flags</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>esc[0].actuator_function=0 (not MOTOR1-based), old timestamp, nonzero current</t>
+          <t>ESC0 esc_current always 0, old timestamp from the start</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>motor stays false, getMotorFailures()=0 [L274-276]</t>
+          <t>no timeout flag, getMotorFailures()=0 [L279,288,298]</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>FD-D31T</t>
+          <t>FD-D32F FD-D33F FD-D35F FD-D36F</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-29</t>
+          <t>SQE-FD-25</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Disarming after an under-current latch clears both the motor flag and the mask</t>
+          <t>Under-current while armed latches the motor flag after the configured timeout</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>FD25 under-current latch sequence, then arming_state=DISARMED, esc_status republished</t>
+          <t>FD_ACT_MOT_THR 0.2, C2T 2.0, TOUT 10ms; ESC0 warmed, then low current w/ high throttle; wait 30ms</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>motor false, getMotorFailures()=0 [L345-352]</t>
+          <t>motor flag true, update() returns true [L313-328]</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>FD-D29F FD-D45</t>
+          <t>FD-D36T FD-D37T FD-D38T FD-D39T FD-D41T</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4243,27 +4243,27 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-30</t>
+          <t>SQE-FD-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::update</t>
+          <t>FailureDetector::updateMotorStatus</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Motor check disabled param skips updateMotorStatus entirely</t>
+          <t>Under-current timer is reset when throttle drops below threshold, and restarts from zero</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>FD_ACT_EN 0; ESC0 with a timed-out stale timestamp and nonzero current</t>
+          <t>FD_ACT_MOT_TOUT 1000ms; timer started; +600ms throttle 0.1 (reset); throttle 0.5 + low current (restart); +600ms check; +500ms control</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>motor stays false, getMotorFailures()=0 (subroutine never called) [L80]</t>
+          <t>motor flag false at t_check although t_check - t_start &gt; 1000ms (proves the reset); true once t - t_restart &gt; 1000ms (restarted timer live). Timing bounds measured and asserted as preconditions (400ms slack) [FailureDetector.cpp L313-327]</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>FD-D05F</t>
+          <t>FD-D38F FD-D40T</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4285,27 +4285,27 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-31</t>
+          <t>SQE-FD-27</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::update + FailureInjector::update/manipulateEscStatus</t>
+          <t>FailureDetector::updateMotorStatus</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>End-to-end: an injected STUCK failure is visible to the detector's own ESC-timeout branch</t>
+          <t>NaN actuator control is treated as zero throttle (guard, not crash)</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; ESC0 warmed; inject STUCK motor instance 1; publish fresh esc_status, update()</t>
+          <t>same params as FD25; actuator_motors.control[0]=NaN with low current</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>motor flag true, getMotorFailures()&amp;1=1 (injector blanked the telemetry the detector then times out) [FailureDetector.cpp L73-82, FailureInjector.cpp L112-134]</t>
+          <t>no under-current timer starts, motor stays false [L305-307]</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -4315,39 +4315,39 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>integration FI-D10/D12 with FD-D33</t>
+          <t>FD-D37F</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector.cpp + FailureInjector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
+          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-32</t>
+          <t>SQE-FD-28</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::update</t>
+          <t>FailureDetector::updateMotorStatus</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>update() return value reflects whether status actually changed</t>
+          <t>Non-motor actuator_function is skipped by the unsigned-wrap guard</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>a no-op update (attitude within limits) vs. a sequence that flips the roll flag</t>
+          <t>esc[0].actuator_function=0 (not MOTOR1-based), old timestamp, nonzero current</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>first call returns false; second returns true [L54,89]</t>
+          <t>motor stays false, getMotorFailures()=0 [L274-276]</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>update() return value (status_prev.value != _status.value)</t>
+          <t>FD-D31T</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -4369,7 +4369,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-33</t>
+          <t>SQE-FD-29</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4379,17 +4379,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>characterization (F-15): disarming after a telemetry-timeout clears motor flag but not the timed-out mask bit</t>
+          <t>Disarming after an under-current latch clears both the motor flag and the mask</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>FD23 steps 1-2 (ESC0 timed out via telemetry timeout); then disarm + republish</t>
+          <t>FD25 under-current latch sequence, then arming_state=DISARMED, esc_status republished</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>motor flag false, but getMotorFailures()&amp;1 still 1 (disarmed reset block never clears _motor_failure_esc_timed_out_mask) [L345-352]</t>
+          <t>motor false, getMotorFailures()=0 [L345-352]</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>FD-D29F characterization</t>
+          <t>FD-D29F FD-D45</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -4411,27 +4411,27 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-34</t>
+          <t>SQE-FD-30</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateAttitudeStatus</t>
+          <t>FailureDetector::update</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Tailsitter rotary-wing applies no rotation before the check (pair of FD10)</t>
+          <t>Motor check disabled param skips updateMotorStatus entirely</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>tailsitter, not in transition, ROTARY_WING; pitch -80 deg settled (same input as FD10)</t>
+          <t>FD_ACT_EN 0; ESC0 with a timed-out stale timestamp and nonzero current</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>pitch flag true (no rotation applied) [L109-115]</t>
+          <t>motor stays false, getMotorFailures()=0 (subroutine never called) [L80]</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>FD-D11F</t>
+          <t>FD-D05F</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -4453,27 +4453,27 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SQE-FDI-01</t>
+          <t>SQE-FD-31</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateImbalancedPropStatus</t>
+          <t>FailureDetector::update + FailureInjector::update/manipulateEscStatus</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Imbalanced accel variance on the selected (first-found) instance sets the flag with the expected filtered metric</t>
+          <t>End-to-end: an injected STUCK failure is visible to the detector's own ESC-timeout branch</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>FD_IMB_PROP_THR 30; selection id 1111; instance0 id 1111 var {40000,40000,0}, ts 10s (first sample, dt clamps to 1s)</t>
+          <t>SYS_FAILURE_EN 1; ESC0 warmed; inject STUCK motor instance 1; publish fresh esc_status, update()</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>imbalanced_prop true; metric ~=33.33 (independent AlphaFilter arithmetic, alpha=1/6) [L220-241]</t>
+          <t>motor flag true, getMotorFailures()&amp;1=1 (injector blanked the telemetry the detector then times out) [FailureDetector.cpp L73-82, FailureInjector.cpp L112-134]</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4483,39 +4483,39 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>FD-D06T FD-D20T FD-D21T FD-D22F FD-D26T FD-D27T FD-D28(T,T)</t>
+          <t>integration FI-D10/D12 with FD-D33</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetectorImu.xml</t>
+          <t>FailureDetector.cpp + FailureInjector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SQE-FDI-02</t>
+          <t>SQE-FD-32</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateImbalancedPropStatus</t>
+          <t>FailureDetector::update</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Equal variances on all 3 axes give a zero metric and no flag</t>
+          <t>update() return value reflects whether status actually changed</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>selection+instance0 id 2222, var {100,100,100}</t>
+          <t>a no-op update (attitude within limits) vs. a sequence that flips the roll flag</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>imbalanced_prop false, metric~=0 [L236]</t>
+          <t>first call returns false; second returns true [L54,89]</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4525,39 +4525,39 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>FD-D28(T,T) threshold F</t>
+          <t>update() return value (status_prev.value != _status.value)</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetectorImu.xml</t>
+          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SQE-FDI-03</t>
+          <t>SQE-FD-33</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::update</t>
+          <t>FailureDetector::updateMotorStatus</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Threshold param 0 disables the whole imbalanced-prop subroutine</t>
+          <t>characterization (F-15): disarming after a telemetry-timeout clears motor flag but not the timed-out mask bit</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>FD_IMB_PROP_THR 0; selection+instance0 with a clearly imbalanced variance</t>
+          <t>FD23 steps 1-2 (ESC0 timed out via telemetry timeout); then disarm + republish</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>flag false, metric stays 0 (updateImbalancedPropStatus never called) [L85]</t>
+          <t>motor flag false, but getMotorFailures()&amp;1 still 1 (disarmed reset block never clears _motor_failure_esc_timed_out_mask) [L345-352]</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -4567,39 +4567,39 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>FD-D06F</t>
+          <t>FD-D29F characterization</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetectorImu.xml</t>
+          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SQE-FDI-04</t>
+          <t>SQE-FD-34</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateImbalancedPropStatus</t>
+          <t>FailureDetector::updateAttitudeStatus</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Selected accel found via the multi-instance search lands on instance 1</t>
+          <t>Tailsitter rotary-wing applies no rotation before the check (pair of FD10)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>selection id 2222; instance0 id 1111 (small var); instance1 id 2222 (large var)</t>
+          <t>tailsitter, not in transition, ROTARY_WING; pitch -80 deg settled (same input as FD10)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>imbalanced_prop true (detected through instance 1) [L205-218]</t>
+          <t>pitch flag true (no rotation applied) [L109-115]</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4609,19 +4609,19 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>FD-D22T FD-D23 FD-D24F FD-D25(F,T)</t>
+          <t>FD-D11F</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetectorImu.xml</t>
+          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SQE-FDI-05</t>
+          <t>SQE-FDI-01</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4631,17 +4631,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Selected accel id present on no instance: search scans all 10, no detection</t>
+          <t>Imbalanced accel variance on the selected (first-found) instance sets the flag with the expected filtered metric</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>selection id 3333 (not on instance0 or instance1)</t>
+          <t>FD_IMB_PROP_THR 30; selection id 1111; instance0 id 1111 var {40000,40000,0}, ts 10s (first sample, dt clamps to 1s)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>imbalanced_prop stays false, metric stays 0 [L207-217]</t>
+          <t>imbalanced_prop true; metric ~=33.33 (independent AlphaFilter arithmetic, alpha=1/6) [L220-241]</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>FD-D24T FD-D28 2nd operand F</t>
+          <t>FD-D06T FD-D20T FD-D21T FD-D22F FD-D26T FD-D27T FD-D28(T,T)</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>SQE-FDI-06</t>
+          <t>SQE-FDI-02</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4673,17 +4673,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Device id 0 (sentinel 'no sensor selected') skips the metric computation even if ids match</t>
+          <t>Equal variances on all 3 axes give a zero metric and no flag</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>selection accel_device_id 0; instance0 accel_device_id 0</t>
+          <t>selection+instance0 id 2222, var {100,100,100}</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>imbalanced_prop stays false, metric stays 0 [L224]</t>
+          <t>imbalanced_prop false, metric~=0 [L236]</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>FD-D22F FD-D28 1st operand F</t>
+          <t>FD-D28(T,T) threshold F</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -4705,27 +4705,27 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>SQE-FDI-07</t>
+          <t>SQE-FDI-03</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateImbalancedPropStatus</t>
+          <t>FailureDetector::update</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>No new selection or IMU publish leaves the filtered metric unchanged</t>
+          <t>Threshold param 0 disables the whole imbalanced-prop subroutine</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>selection+instance0 published once, consumed; second update() without new publishes</t>
+          <t>FD_IMB_PROP_THR 0; selection+instance0 with a clearly imbalanced variance</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>metric unchanged [L191,199]</t>
+          <t>flag false, metric stays 0 (updateImbalancedPropStatus never called) [L85]</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>FD-D20F FD-D26F</t>
+          <t>FD-D06F</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -4747,27 +4747,27 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-01</t>
+          <t>SQE-FDI-04</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector::update</t>
+          <t>FailureDetector::updateImbalancedPropStatus</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Injection disabled at construction: command has no effect and no ack is published</t>
+          <t>Selected accel found via the multi-instance search lands on instance 1</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 0; inject OFF motor instance 1; update()</t>
+          <t>selection id 2222; instance0 id 1111 (small var); instance1 id 2222 (large var)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>getMotorStopMask()=0, no ack published [L51]</t>
+          <t>imbalanced_prop true (detected through instance 1) [L205-218]</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -4777,39 +4777,39 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>FI-D01 2nd operand F; FI-D02T</t>
+          <t>FD-D22T FD-D23 FD-D24F FD-D25(F,T)</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector.cpp ; evidence/tests/xml/functional-SqeFailureInjector.xml</t>
+          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetectorImu.xml</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-02</t>
+          <t>SQE-FDI-05</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector::update</t>
+          <t>FailureDetector::updateImbalancedPropStatus</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>OFF injected for a specific motor instance sets the stop mask bit and acks ACCEPTED</t>
+          <t>Selected accel id present on no instance: search scans all 10, no detection</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; OFF instance 1 (ESC index 0)</t>
+          <t>selection id 3333 (not on instance0 or instance1)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>getMotorStopMask()=0x01; ack command=420, result=ACCEPTED [L67-108]</t>
+          <t>imbalanced_prop stays false, metric stays 0 [L207-217]</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -4819,39 +4819,39 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>FI-D01T FI-D03 FI-D04F FI-D05 FI-D06 FI-D07(OFF) FI-D08T</t>
+          <t>FD-D24T FD-D28 2nd operand F</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector.cpp ; evidence/tests/xml/functional-SqeFailureInjector.xml</t>
+          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetectorImu.xml</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-03</t>
+          <t>SQE-FDI-06</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector::update</t>
+          <t>FailureDetector::updateImbalancedPropStatus</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Instance 0 means 'apply to all ESCs'</t>
+          <t>Device id 0 (sentinel 'no sensor selected') skips the metric computation even if ids match</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; OFF instance 0</t>
+          <t>selection accel_device_id 0; instance0 accel_device_id 0</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>getMotorStopMask()=0xFF (all 8 bits) [L68]</t>
+          <t>imbalanced_prop stays false, metric stays 0 [L224]</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4861,39 +4861,39 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>FI-D06 1st operand F</t>
+          <t>FD-D22F FD-D28 1st operand F</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector.cpp ; evidence/tests/xml/functional-SqeFailureInjector.xml</t>
+          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetectorImu.xml</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-04</t>
+          <t>SQE-FDI-07</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector::update/manipulateEscStatus</t>
+          <t>FailureDetector::updateImbalancedPropStatus</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>OK clears both the stop mask and the telemetry-blocked/wrong masks</t>
+          <t>No new selection or IMU publish leaves the filtered metric unchanged</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>OFF(1) then OK(1); STUCK(2) then OK(2), one update() per command</t>
+          <t>selection+instance0 published once, consumed; second update() without new publishes</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>getMotorStopMask()=0; manipulateEscStatus() leaves a 2-ESC status unchanged [L73-79]</t>
+          <t>metric unchanged [L191,199]</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4903,39 +4903,39 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>FI-D07(OK)</t>
+          <t>FD-D20F FD-D26F</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector.cpp ; evidence/tests/xml/functional-SqeFailureInjector.xml</t>
+          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetectorImu.xml</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-05</t>
+          <t>SQE-FI-01</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector::manipulateEscStatus</t>
+          <t>FailureInjector::update</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>STUCK blanks only the targeted ESC's telemetry and its online-flag bit</t>
+          <t>Injection disabled at construction: command has no effect and no ack is published</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; STUCK instance 2 (ESC index 1); 4-ESC status, esc_online_flags 0xFF seed</t>
+          <t>SYS_FAILURE_EN 0; inject OFF motor instance 1; update()</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>esc[1] zeroed except actuator_function; esc_online_flags=0xFD (bit1 cleared); esc[0,2,3] unchanged [L116-124]</t>
+          <t>getMotorStopMask()=0, no ack published [L51]</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>FI-D07(STUCK) FI-D10T FI-D11 FI-D12T</t>
+          <t>FI-D01 2nd operand F; FI-D02T</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -4957,27 +4957,27 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-06</t>
+          <t>SQE-FI-02</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector::manipulateEscStatus</t>
+          <t>FailureInjector::update</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>WRONG scales voltage/current down and rpm up on the targeted ESC</t>
+          <t>OFF injected for a specific motor instance sets the stop mask bit and acks ACCEPTED</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; WRONG instance 1 (ESC index 0); voltage 10, current 2, rpm 1000</t>
+          <t>SYS_FAILURE_EN 1; OFF instance 1 (ESC index 0)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>voltage*0.1=1, current*0.1=0.2, rpm*10=10000 [L126-130]</t>
+          <t>getMotorStopMask()=0x01; ack command=420, result=ACCEPTED [L67-108]</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>FI-D07(WRONG) FI-D13T</t>
+          <t>FI-D01T FI-D03 FI-D04F FI-D05 FI-D06 FI-D07(OFF) FI-D08T</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-07</t>
+          <t>SQE-FI-03</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5009,17 +5009,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>An unrecognised failure_type (GARBAGE) leaves 'supported' false and masks unchanged</t>
+          <t>Instance 0 means 'apply to all ESCs'</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; failure_type GARBAGE (3, no matching switch case)</t>
+          <t>SYS_FAILURE_EN 1; OFF instance 0</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>ack result UNSUPPORTED; getMotorStopMask()=0 [L72-98,104-106]</t>
+          <t>getMotorStopMask()=0xFF (all 8 bits) [L68]</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>FI-D07(no case) FI-D08F</t>
+          <t>FI-D06 1st operand F</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5041,27 +5041,27 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-08</t>
+          <t>SQE-FI-04</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector::update</t>
+          <t>FailureInjector::update/manipulateEscStatus</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>A non-INJECT_FAILURE command is skipped: no ack, no mask change</t>
+          <t>OK clears both the stop mask and the telemetry-blocked/wrong masks</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; DO_SET_MODE command published</t>
+          <t>OFF(1) then OK(1); STUCK(2) then OK(2), one update() per command</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>getMotorStopMask()=0, no ack [L59-62]</t>
+          <t>getMotorStopMask()=0; manipulateEscStatus() leaves a 2-ESC status unchanged [L73-79]</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>FI-D04 1st operand T</t>
+          <t>FI-D07(OK)</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5083,27 +5083,27 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-09</t>
+          <t>SQE-FI-05</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector::update</t>
+          <t>FailureInjector::manipulateEscStatus</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>A failure_unit other than SYSTEM_MOTOR is skipped: no ack, no mask change</t>
+          <t>STUCK blanks only the targeted ESC's telemetry and its online-flag bit</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; INJECT_FAILURE with unit FAILURE_UNIT_SENSOR_GYRO(0)</t>
+          <t>SYS_FAILURE_EN 1; STUCK instance 2 (ESC index 1); 4-ESC status, esc_online_flags 0xFF seed</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>getMotorStopMask()=0, no ack [L59-62]</t>
+          <t>esc[1] zeroed except actuator_function; esc_online_flags=0xFD (bit1 cleared); esc[0,2,3] unchanged [L116-124]</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>FI-D04 2nd operand T</t>
+          <t>FI-D07(STUCK) FI-D10T FI-D11 FI-D12T</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5125,27 +5125,27 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-10</t>
+          <t>SQE-FI-06</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector::update</t>
+          <t>FailureInjector::manipulateEscStatus</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Instance beyond the ESC range matches nothing: ack UNSUPPORTED</t>
+          <t>WRONG scales voltage/current down and rpm up on the targeted ESC</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; OFF instance 9 (no i in [0,8) satisfies i==8)</t>
+          <t>SYS_FAILURE_EN 1; WRONG instance 1 (ESC index 0); voltage 10, current 2, rpm 1000</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>getMotorStopMask()=0; ack UNSUPPORTED [L67-70,104-106]</t>
+          <t>voltage*0.1=1, current*0.1=0.2, rpm*10=10000 [L126-130]</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>FI-D06 all continue</t>
+          <t>FI-D07(WRONG) FI-D13T</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -5167,27 +5167,27 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-11</t>
+          <t>SQE-FI-07</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector::manipulateEscStatus</t>
+          <t>FailureInjector::update</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Injection disabled at construction: manipulateEscStatus is a no-op</t>
+          <t>An unrecognised failure_type (GARBAGE) leaves 'supported' false and masks unchanged</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 0; manipulateEscStatus() called directly on a populated status</t>
+          <t>SYS_FAILURE_EN 1; failure_type GARBAGE (3, no matching switch case)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>status completely unchanged (early return) [L114]</t>
+          <t>ack result UNSUPPORTED; getMotorStopMask()=0 [L72-98,104-106]</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>FI-D09T</t>
+          <t>FI-D07(no case) FI-D08F</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -5209,27 +5209,27 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-12</t>
+          <t>SQE-FI-08</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector::manipulateEscStatus</t>
+          <t>FailureInjector::update</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Enabled but no failures injected yet: manipulateEscStatus is a no-op</t>
+          <t>A non-INJECT_FAILURE command is skipped: no ack, no mask change</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; no injection commands ever sent; manipulateEscStatus() called</t>
+          <t>SYS_FAILURE_EN 1; DO_SET_MODE command published</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>status unchanged (blocked_mask==0 &amp;&amp; wrong_mask==0) [L116]</t>
+          <t>getMotorStopMask()=0, no ack [L59-62]</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>FI-D10F</t>
+          <t>FI-D04 1st operand T</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>SQE-FI-13</t>
+          <t>SQE-FI-09</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5261,17 +5261,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Multiple queued commands are all drained in a single update() call</t>
+          <t>A failure_unit other than SYSTEM_MOTOR is skipped: no ack, no mask change</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; OFF(1) and STUCK(2) both published before one update()</t>
+          <t>SYS_FAILURE_EN 1; INJECT_FAILURE with unit FAILURE_UNIT_SENSOR_GYRO(0)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>getMotorStopMask()=0x01 and esc[1] zeroed by manipulateEscStatus (both applied) [L55 while loop]</t>
+          <t>getMotorStopMask()=0, no ack [L59-62]</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>FI-D03 multi-iteration</t>
+          <t>FI-D04 2nd operand T</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -5293,49 +5293,49 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>SQE-PRB-05</t>
+          <t>SQE-FI-10</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector::manipulateEscStatus</t>
+          <t>FailureInjector::update</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>probe (F-07a): esc_count above CONNECTED_ESC_MAX has no bounds clamp unlike the sibling loop</t>
+          <t>Instance beyond the ESC range matches nothing: ack UNSUPPORTED</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; STUCK instance 1; esc_count forced to 9 (fixed esc[8] array)</t>
+          <t>SYS_FAILURE_EN 1; OFF instance 9 (no i in [0,8) satisfies i==8)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>under ASan: the probe aborts with stack-buffer-overflow, READ at FailureInjector.cpp:118 (status.esc[8], one past the esc[8] array) -&gt; F-07a defect present. In a normal/Coverage build the probe is an inert SUCCEED() and proves nothing</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>getMotorStopMask()=0; ack UNSUPPORTED [L67-70,104-106]</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>FI-D11 no clamp</t>
+          <t>FI-D06 all continue</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector.cpp ; sanitizer run: evidence/tests/sanitizer/asan_PRB05.log (ASan stack-buffer-overflow at FailureInjector.cpp:118; reproduce with tools/sqe_asan_probes.sh) -- fails as expected, defect F-07a confirmed at runtime</t>
+          <t>FailureInjector.cpp ; evidence/tests/xml/functional-SqeFailureInjector.xml</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SQE-PRB-06</t>
+          <t>SQE-FI-11</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5345,59 +5345,59 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>probe (F-07b): non-motor actuator_function causes an unguarded shift exponent in the blocked-mask check</t>
+          <t>Injection disabled at construction: manipulateEscStatus is a no-op</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>SYS_FAILURE_EN 1; STUCK instance 1; esc[0].actuator_function=0 (not MOTOR1-based)</t>
+          <t>SYS_FAILURE_EN 0; manipulateEscStatus() called directly on a populated status</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>under UBSan (-fsanitize=shift): 'shift exponent 4294967195 is too large for 32-bit type int' at FailureInjector.cpp:120 -&gt; F-07b defect present. In a normal/Coverage build the probe is an inert SUCCEED() and proves nothing</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>status completely unchanged (early return) [L114]</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>FI-D12 no guard</t>
+          <t>FI-D09T</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>FailureInjector.cpp ; sanitizer run: evidence/tests/sanitizer/ubsan_PRB06.log (UBSan shift-exponent runtime error at FailureInjector.cpp:120; reproduce with tools/sqe_ubsan_probes.sh) -- fails as expected, defect F-07b confirmed at runtime</t>
+          <t>FailureInjector.cpp ; evidence/tests/xml/functional-SqeFailureInjector.xml</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-36</t>
+          <t>SQE-FI-12</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateMotorStatus</t>
+          <t>FailureInjector::manipulateEscStatus</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>FD-D38 3rd operand False (esc_timed_out True while throttle_above_threshold and current_too_low are also True)</t>
+          <t>Enabled but no failures injected yet: manipulateEscStatus is a no-op</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>ESC0 warmed up; actuator control above threshold; esc_current low AND esc[0].timestamp stale (&gt;300ms old) in the same sample</t>
+          <t>SYS_FAILURE_EN 1; no injection commands ever sent; manipulateEscStatus() called</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>under-current timer not armed by this sample (mask bit stays 0 for the under-current path); motor flag true only via the independent ESC-timeout path (FD-D33) [L313]</t>
+          <t>status unchanged (blocked_mask==0 &amp;&amp; wrong_mask==0) [L116]</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5407,39 +5407,39 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>FD-D38F</t>
+          <t>FI-D10F</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
+          <t>FailureInjector.cpp ; evidence/tests/xml/functional-SqeFailureInjector.xml</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>SQE-FD-37</t>
+          <t>SQE-FI-13</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector::updateMotorStatus</t>
+          <t>FailureInjector::update</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>FD-D41 3rd operand False (under-current mask bit already set from a prior latch)</t>
+          <t>Multiple queued commands are all drained in a single update() call</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>FD25-style first latch sets the under-current mask bit; a second full under-current cycle (timer reset via throttle drop, then re-armed and expired again) re-evaluates the decision with the bit already 1</t>
+          <t>SYS_FAILURE_EN 1; OFF(1) and STUCK(2) both published before one update()</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>getMotorFailures() and motor flag unchanged across the second expiry (idempotent OR on an already-set bit) [L324-326]</t>
+          <t>getMotorStopMask()=0x01 and esc[1] zeroed by manipulateEscStatus (both applied) [L55 while loop]</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -5449,59 +5449,227 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>FD-D41F</t>
+          <t>FI-D03 multi-iteration</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
+          <t>FailureInjector.cpp ; evidence/tests/xml/functional-SqeFailureInjector.xml</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>SQE-PRB-05</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>FailureInjector::manipulateEscStatus</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>probe (F-07a): esc_count above CONNECTED_ESC_MAX has no bounds clamp unlike the sibling loop</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>SYS_FAILURE_EN 1; STUCK instance 1; esc_count forced to 9 (fixed esc[8] array)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>under ASan: the probe aborts with stack-buffer-overflow, READ at FailureInjector.cpp:118 (status.esc[8], one past the esc[8] array) -&gt; F-07a defect present. In a normal/Coverage build the probe is an inert SUCCEED() and proves nothing</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>FI-D11 no clamp</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>FailureInjector.cpp ; sanitizer run: evidence/tests/sanitizer/asan_PRB05.log (ASan stack-buffer-overflow at FailureInjector.cpp:118; reproduce with tools/sqe_asan_probes.sh) -- fails as expected, defect F-07a confirmed at runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>SQE-PRB-06</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>FailureInjector::manipulateEscStatus</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>probe (F-07b): non-motor actuator_function causes an unguarded shift exponent in the blocked-mask check</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>SYS_FAILURE_EN 1; STUCK instance 1; esc[0].actuator_function=0 (not MOTOR1-based)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>under UBSan (-fsanitize=shift): 'shift exponent 4294967195 is too large for 32-bit type int' at FailureInjector.cpp:120 -&gt; F-07b defect present. In a normal/Coverage build the probe is an inert SUCCEED() and proves nothing</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>FI-D12 no guard</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>FailureInjector.cpp ; sanitizer run: evidence/tests/sanitizer/ubsan_PRB06.log (UBSan shift-exponent runtime error at FailureInjector.cpp:120; reproduce with tools/sqe_ubsan_probes.sh) -- fails as expected, defect F-07b confirmed at runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>SQE-FD-36</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>FailureDetector::updateMotorStatus</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>FD-D38 3rd operand False (esc_timed_out True while throttle_above_threshold and current_too_low are also True)</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>ESC0 warmed up; actuator control above threshold; esc_current low AND esc[0].timestamp stale (&gt;300ms old) in the same sample</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>under-current timer not armed by this sample (mask bit stays 0 for the under-current path); motor flag true only via the independent ESC-timeout path (FD-D33) [L313]</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>FD-D38F</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>SQE-FD-37</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>FailureDetector::updateMotorStatus</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>FD-D41 3rd operand False (under-current mask bit already set from a prior latch)</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>FD25-style first latch sets the under-current mask bit; a second full under-current cycle (timer reset via throttle drop, then re-armed and expired again) re-evaluates the decision with the bit already 1</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>getMotorFailures() and motor flag unchanged across the second expiry (idempotent OR on an already-set bit) [L324-326]</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>FD-D41F</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetector.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
           <t>SQE-FDI-08</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>FailureDetector::updateImbalancedPropStatus</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>FD-D25 1st operand False (copy() fails on an advertised-but-never-published uORB instance)</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>a 3rd PublicationMulti&lt;vehicle_imu_status_s&gt; calls advertise() but never publish() (lands on instance 2); selection id matches neither instance 0 nor 1</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>no crash; instance search continues past instance 2 (ChangeInstance succeeds, copy() fails); imbalanced_prop stays false [L212-213]</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>FD-D25F</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>FailureDetector.cpp ; evidence/tests/xml/functional-SqeFailureDetectorImu.xml</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H117"/>
+  <autoFilter ref="A1:H121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/deliverables/24i3015_24i3166_24i3158_B.xlsx
+++ b/deliverables/24i3015_24i3166_24i3158_B.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MC-DC Evidence" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Inventory'!$A$1:$H$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Inventory'!$A$1:$H$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MC-DC Evidence'!$A$1:$S$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40,7 +40,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +63,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+        <bgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -110,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -131,6 +137,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -573,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5500,8 +5509,134 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>SQE-DVG-AF-01</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>DataValidatorGroup::add_new_validator</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>DVG-D05 True (allocation failure on add_new_validator's own `new DataValidator()`), closes gap G-01's add_new_validator half</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>GCC operator-new-override fault injection (SPEC_02 S9): next heap allocation armed to fail via g_fail_countdown=0, then add_new_validator() called on a healthy DataValidatorGroup(1)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>add_new_validator() returns nullptr per its documented @return contract; group unchanged (get_sensor_state(1) stays UINT32_MAX, sensor 0 untouched) [DataValidatorGroup.cpp L88-89]</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>DVG-D05T</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>DataValidatorGroup.cpp ; evidence/tests/xml/unit-SqeDataValidatorAllocFault.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>SQE-DVG-AF-02</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>DataValidatorGroup::DataValidatorGroup (constructor)</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>characterization: constructor's first-allocation-fails path has no null guard at all, unlike add_new_validator()</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>same fault-injection technique; first heap allocation armed to fail (i=0 of siblings=2), then DataValidatorGroup(2) constructed</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>process crashes (SIGSEGV) -- traced to `prev-&gt;setSibling(next)` at the i=1 loop iteration dereferencing prev==nullptr (not `_first-&gt;get_timeout()`, which IS guarded by `if (_first)`); confirmed via EXPECT_DEATH [DataValidatorGroup.cpp L48-65]</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>DVG-D05 (constructor path)</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>DataValidatorGroup.cpp ; evidence/tests/xml/unit-SqeDataValidatorAllocFault.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>SQE-DVG-AF-00</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>DataValidatorGroup (compile-time platform guard)</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>non-decision: compiler-guard placeholder, not a coverage/decision target</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>compiled only on non-GCC toolchains (Clang/other) -- never executes on this session's GCC build</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>GTEST_SKIP() with an explanatory message</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>NOT EXECUTED — always-skipped on GCC builds (this session's platform); exists only so the file compiles and names a target on non-GCC toolchains instead of silently vanishing, per SPEC_02 S9's Clang guidance</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>none (platform guard)</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>DataValidatorGroup.cpp ; no XML (manual status)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H117"/>
+  <autoFilter ref="A1:H120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -5665,42 +5800,42 @@
           <t>call2,i=1 (m=.95,mp=50,c=.95,p=75)</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -5762,42 +5897,42 @@
           <t>call2,i=1 (m=.95,mp=50,c=.95,p=50)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -5859,42 +5994,42 @@
           <t>call2,i=1 (m=.95,mp=50,c=.93,p=75)</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -5956,42 +6091,42 @@
           <t>call2,i=1 (m=.95,mp=50,c=.97,p=50)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -6053,42 +6188,42 @@
           <t>call2,i=1 (m=.95,mp=50,c=.97,p=25)</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -6150,42 +6285,42 @@
           <t>call2,i=1 (m=.95,mp=50,c=.93,p=50)</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -6247,42 +6382,42 @@
           <t>call2,i=1 (m=.89,mp=50,c=.95,p=25)</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr">
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -6344,42 +6479,42 @@
           <t>call2,i=1 (m=.91,mp=50,c=.95,p=25)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -6441,42 +6576,42 @@
           <t>call2,i=1 (m=.80,mp=50,c=.95,p=25)</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -6538,42 +6673,42 @@
           <t>call2,i=1 (m=.80,mp=50,c=.85,p=25)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -6635,42 +6770,42 @@
           <t>call1,i=0 (m=-1,mp=-1000,c=0,p=0)</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -6732,42 +6867,42 @@
           <t>call1,i=0 (m=-1,mp=-1000,c=.50,p=50)</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -6829,17 +6964,17 @@
           <t>call3 (switch 0-&gt;1 after sensor0 TIMEOUT)</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>NE(F)</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
@@ -6848,7 +6983,7 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -6910,17 +7045,17 @@
           <t>call2 (stable, sensor0 keeps winning on priority)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
@@ -6929,7 +7064,7 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -6991,17 +7126,17 @@
           <t>call2 (single sensor, fresh data, stable)</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
@@ -7010,7 +7145,7 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N16" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -7064,17 +7199,17 @@
           <t>call3 (single sensor silent &gt; timeout)</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -7083,7 +7218,7 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="N17" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -7145,17 +7280,17 @@
           <t>call1 (single sensor never fed)</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -7164,7 +7299,7 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="N18" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -7218,17 +7353,17 @@
           <t>call2 (equal-confidence, higher-priority switch -- D14 True there via H)</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -7237,7 +7372,7 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="N19" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -7299,17 +7434,17 @@
           <t>call2 (strictly-better-confidence, equal-priority switch -- D14 True there via H)</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
@@ -7318,7 +7453,7 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N20" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -7380,17 +7515,17 @@
           <t>call2 (equal/higher priority but confidence drops by &gt;=0.1 -- D14 True there via H)</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -7399,7 +7534,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N21" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -7461,17 +7596,17 @@
           <t>call1 (very first get_best(), D14 True via H alone -- K-false control vector)</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
@@ -7480,7 +7615,7 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="N22" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -7542,17 +7677,17 @@
           <t>failover_index()/failover_state() after real failover, i=0</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -7561,7 +7696,7 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr">
+      <c r="N23" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -7623,17 +7758,17 @@
           <t>failover_index()/failover_state() after sensor0 recovers, i=0</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
@@ -7642,7 +7777,7 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="N24" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -7704,17 +7839,17 @@
           <t>failover_index()/failover_state() -- sensor timed out but never was best, i=1</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -7723,7 +7858,7 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="N25" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -7785,17 +7920,17 @@
           <t>failover_index()/failover_state(), continuing MC13's state -- put() with timestamp=0 resets used(), i=0</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
@@ -7804,7 +7939,7 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="N26" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -7866,17 +8001,17 @@
           <t>failover_state() (same scenario as D32, different getter) after real failover, i=0</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -7885,7 +8020,7 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr">
+      <c r="N27" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -7947,17 +8082,17 @@
           <t>failover_state() (same scenario as D32, different getter) after sensor0 recovers, i=0</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
@@ -7966,7 +8101,7 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="N28" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -8028,17 +8163,17 @@
           <t>failover_state() (same scenario as D32, different getter) -- sensor timed out but never was best, i=1</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -8047,7 +8182,7 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="N29" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -8109,17 +8244,17 @@
           <t>failover_state() (same scenario as D32, different getter) -- put() with timestamp=0 resets used(), i=0</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>NE(T)</t>
         </is>
@@ -8128,7 +8263,7 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="N30" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
